--- a/frontend/data/suggestions.xlsx
+++ b/frontend/data/suggestions.xlsx
@@ -161,7 +161,7 @@
     <t>doctor.search</t>
   </si>
   <si>
-    <t>건강 정보</t>
+    <t>건강검진 안내</t>
   </si>
   <si>
     <t>info.health</t>
